--- a/Organization_Template_Alternate_example_data.xlsx
+++ b/Organization_Template_Alternate_example_data.xlsx
@@ -16,8 +16,7 @@
     <sheet name="Contact people" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Interfaces" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Vendor info" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Notes" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Accounts" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Accounts" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -1083,72 +1082,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16.140625" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Migrated from legacy ERP system on initial load; verify accounts before go-live.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Confirm billing contact with vendor before the October renewal cycle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NORTHWIND</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Contract discontinued; retained for historical order records only.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/Organization_Template_Alternate_example_data.xlsx
+++ b/Organization_Template_Alternate_example_data.xlsx
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
       <c r="I1" s="28" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Billing</t>
+          <t>Billing;Shipping</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
       <c r="E1" s="28" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Sales;Support</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
       <c r="E1" s="28" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Sales;Marketing</t>
         </is>
       </c>
     </row>
@@ -3633,13 +3633,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.140625" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -3661,10 +3661,15 @@
       </c>
       <c r="D1" s="28" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>NOTE</t>
         </is>
       </c>
       <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>CATEGORIES</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
         </is>
@@ -3688,10 +3693,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Requires vendor portal login credentials</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
+        <is>
+          <t>Support;Sales</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3715,7 +3725,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Only accessible to registered support accounts</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Support;Technical</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3750,7 @@
           <t>Publisher homepage</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3752,7 +3767,12 @@
           <t>https://www.northwindtraders.example</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Domain expired; vendor confirmed inactive</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3769,7 +3789,7 @@
           <t>https://www.acmebinding.example</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3786,7 +3806,7 @@
           <t>https://www.brepols.example</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3803,7 +3823,7 @@
           <t>https://www.oclc.example</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3820,7 +3840,7 @@
           <t>https://www.follett.example</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3837,7 +3857,7 @@
           <t>https://www.ingramlibrary.example</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3854,7 +3874,7 @@
           <t>https://www.baker-taylor.example</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3871,7 +3891,7 @@
           <t>https://www.metrodigital.example</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3933,12 +3953,12 @@
           <t>NOTES</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PHONE </t>
         </is>
@@ -3950,7 +3970,7 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -3997,7 +4017,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Renewals</t>
+          <t>Renewals;Support</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4315,7 @@
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
@@ -4315,12 +4335,12 @@
           <t>DELIVERY METHOD</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="31" t="inlineStr">
         <is>
           <t>USERNAME</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="31" t="inlineStr">
         <is>
           <t>PASSWORD</t>
         </is>

--- a/Organization_Template_Alternate_example_data.xlsx
+++ b/Organization_Template_Alternate_example_data.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Interfaces" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Vendor info" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Accounts" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="External note" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -1448,6 +1449,158 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.57" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>ORG CODE</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>NOTE TYPE</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>NOTE TITLE</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>CONTENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EBSCO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Account overview</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Long-standing subscription agent; primary contact is Jan Novak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EBSCO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Follow-up</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Renewal timing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Renewal negotiations typically start in Q3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ELSEVIER</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Contract terms</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Reviewing multi-year contract terms currently in effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NORTHWIND</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Contract discontinued</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Vendor relationship ended 2024; retained for historical records only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OCLC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Service scope</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Provides cataloging and resource-sharing services across the consortium.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3913,7 +4066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3945,30 +4098,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>TITLE</t>
+          <t>NOTES</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>NOTES</t>
+          <t>EMAIL</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>EMAIL</t>
+          <t xml:space="preserve">PHONE </t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHONE </t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
@@ -3992,30 +4140,25 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Account Manager</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
           <t>Prefers email over phone</t>
         </is>
       </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>jnovak@ebsco.com</t>
+        </is>
+      </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>jnovak@ebsco.com</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
           <t>555-201-0001</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Renewals contact</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Renewals;Support</t>
         </is>
@@ -4037,23 +4180,18 @@
           <t>Mario</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Support Specialist</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>mrossi@ebsco.com</t>
+        </is>
+      </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>mrossi@ebsco.com</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
           <t>555-201-0002</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Technical support contact</t>
         </is>
@@ -4075,22 +4213,17 @@
           <t>Anke</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Customer Success Manager</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>a.devries@elsevier.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>a.devries@elsevier.com</t>
+          <t>+31-20-4853700</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>+31-20-4853700</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>Primary account contact</t>
         </is>
@@ -4114,25 +4247,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rights Manager</t>
+          <t>Contract ended 2024, contact for archival questions only</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Contract ended 2024, contact for archival questions only</t>
+          <t>fmacdonald@northwindtraders.example</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>fmacdonald@northwindtraders.example</t>
+          <t>902-555-0111</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>902-555-0111</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t>Rights and permissions contact</t>
         </is>
@@ -4154,22 +4282,17 @@
           <t>Wei</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Operations Manager</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>wchen@acmebinding.example</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>wchen@acmebinding.example</t>
+          <t>614-555-0135</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>614-555-0135</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>Scheduling and logistics</t>
         </is>
@@ -4191,22 +4314,17 @@
           <t>Lena</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>l.peeters@brepols.example</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>l.peeters@brepols.example</t>
+          <t>+32-14-448021</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>+32-14-448021</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
         <is>
           <t>Regional sales contact</t>
         </is>
@@ -4228,22 +4346,17 @@
           <t>Diego</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Volunteer Coordinator</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>dalvarez@riversidebooks.example</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>dalvarez@riversidebooks.example</t>
+          <t>951-555-0198</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>951-555-0198</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
         <is>
           <t>Donations contact</t>
         </is>
@@ -4265,22 +4378,17 @@
           <t>Tam</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Account Executive</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tnguyen@metrodigital.example</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>tnguyen@metrodigital.example</t>
+          <t>916-555-0143</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
-        <is>
-          <t>916-555-0143</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
         <is>
           <t>Primary sales contact</t>
         </is>

--- a/Organization_Template_Alternate_example_data.xlsx
+++ b/Organization_Template_Alternate_example_data.xlsx
@@ -1455,7 +1455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.57" customWidth="1" min="1" max="1"/>
@@ -1593,6 +1593,28 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>Provides cataloging and resource-sharing services across the consortium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BAKERTAYLOR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Migration test</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Data load verification</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Added to confirm a brand-new note type is created in FOLIO and notes.json typeId is remapped to its real id on load.</t>
         </is>
       </c>
     </row>

--- a/Organization_Template_Alternate_example_data.xlsx
+++ b/Organization_Template_Alternate_example_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-37452" yWindow="10548" windowWidth="21744" windowHeight="11844" tabRatio="731" firstSheet="8" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1650" yWindow="1455" windowWidth="25050" windowHeight="13140" tabRatio="731" firstSheet="1" activeTab="11" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="How to use this workbook" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,14 +20,14 @@
     <sheet name="External note" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,22 +90,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <charset val="1"/>
-      <color theme="1"/>
-      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
-      <charset val="1"/>
-      <color rgb="FF242424"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Source Sans Pro"/>
-      <i val="1"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -164,7 +161,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -177,39 +174,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
@@ -218,13 +192,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,7 +597,7 @@
   <dimension ref="B2:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.140625" customWidth="1" min="2" max="2"/>
+    <col width="12.140625" customWidth="1" style="24" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -638,14 +629,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Go to Main Org record sheet</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Please note that coloured columns are mandatory.</t>
         </is>
@@ -654,7 +645,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>This applies on every sheet, not just Main Org record - e.g. PHONE on the Phones sheet, EMAIL on the Emails sheet, ACCOUNT NAME/ACCOUNT NUMBER/ACCOUNT STATUS on the Accounts sheet. One exception: an interface's USERNAME/PASSWORD (on the Interfaces sheet) aren't colored as mandatory since an interface doesn't need login credentials at all - but if you fill in either one, you must fill in both, or just that login-credentials record is skipped (the interface itself, and the rest of that organization, still build normally).</t>
+          <t>This applies on every sheet, not just Main Org record - e.g. PHONE on the Phones sheet, EMAIL on the Emails sheet, ACCOUNT NAME/ACCOUNT NUMBER/ACCOUNT STATUS on the Accounts sheet. A colored column can also be a 'required if you use this at all' pair rather than a plain single field: an interface's USERNAME/PASSWORD (on the Interfaces sheet) are both colored because if you fill in either one, you must fill in both, or just that login-credentials record is skipped (the interface itself, and the rest of that organization, still build normally). The Interfaces sheet's own NAME column, on the other hand, is intentionally NOT colored - the real FOLIO interface record has no required fields of its own, not even a name.</t>
         </is>
       </c>
     </row>
@@ -686,172 +677,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14.42578125" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="14"/>
+    <col width="14.42578125" customWidth="1" style="24" min="1" max="1"/>
+    <col width="15" customWidth="1" style="24" min="2" max="10"/>
+    <col width="15" customWidth="1" style="12" min="11" max="11"/>
+    <col width="15" customWidth="1" style="24" min="12" max="13"/>
+    <col width="15" customWidth="1" style="12" min="14" max="14"/>
+    <col width="11.42578125" bestFit="1" customWidth="1" style="24" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="27" t="inlineStr">
+    <row r="1" ht="60" customHeight="1" s="24">
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>Pipe delimited (|) list of currencies permitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1" s="24">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>PAYMENT METHOD</t>
         </is>
       </c>
-      <c r="C1" s="27" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>CURRENCIES</t>
         </is>
       </c>
-      <c r="D1" s="27" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>CLAIMING INTERVAL</t>
         </is>
       </c>
-      <c r="E1" s="27" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>DISCOUNT %</t>
         </is>
       </c>
-      <c r="F1" s="27" t="inlineStr">
-        <is>
-          <t>EXP ACTIVATION INTERVAL</t>
-        </is>
-      </c>
-      <c r="G1" s="27" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>EXPECTED ACTIVATION INTERVAL</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>EXP INVOICE INTERVAL</t>
         </is>
       </c>
-      <c r="H1" s="27" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>EXP RECEIPT INTERVAL</t>
         </is>
       </c>
-      <c r="I1" s="27" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>RENEWAL ACTIVATION INTERVAL</t>
         </is>
       </c>
-      <c r="J1" s="27" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>SUBSCRIPTION INTERVAL</t>
         </is>
       </c>
-      <c r="K1" s="27" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>EXPORT TO ACCOUNTING (Y/)</t>
         </is>
       </c>
-      <c r="L1" s="27" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>TAX ID</t>
         </is>
       </c>
-      <c r="M1" s="27" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>TAX %</t>
         </is>
       </c>
-      <c r="N1" s="27" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>LIABLE FOR VAT (Y/N)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>EFT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>USD|EUR</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J2" t="n">
-        <v>365</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>04-1667882</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Do not edit:</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELSEVIER</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>EFT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
+          <t>USD|EUR</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" t="n">
+        <v>365</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>12-3456789</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -861,15 +846,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CAD</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>45</v>
       </c>
       <c r="K4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -878,12 +861,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ACMEBIND</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank Draft</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -891,6 +874,12 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -898,11 +887,8 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>31-9988776</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>7.5</v>
+          <t>98-7654321</t>
+        </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -913,34 +899,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BREPOLS</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EFT</t>
+          <t>Bank Draft</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>SUMMITDATA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -953,26 +945,55 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="n">
+        <v>365</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>55-1122334</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>6</v>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FOLLETT</t>
+          <t>LONESTARPUB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Physical Check</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -980,12 +1001,10 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
       <c r="K8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -994,7 +1013,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INGRAM</t>
+          <t>BLUEHORIZON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1007,10 +1026,24 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D9" t="n">
+        <v>45</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>44-9988776</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1021,12 +1054,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BAKERTAYLOR</t>
+          <t>SILVERLAKE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Physical Check</t>
+          <t>EFT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1034,9 +1067,17 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>33-4455667</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1048,7 +1089,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>METRODS</t>
+          <t>TIMBERLINE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1061,18 +1102,24 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="K3:K1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>$AA$2:$AA$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="N3:N1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1083,217 +1130,149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A2:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.28515625" customWidth="1" style="20" min="1" max="1"/>
-    <col width="22.140625" customWidth="1" min="2" max="2"/>
-    <col width="20.85546875" customWidth="1" min="3" max="3"/>
-    <col width="36.5703125" customWidth="1" min="4" max="4"/>
-    <col width="24.5703125" customWidth="1" min="5" max="6"/>
-    <col width="25.85546875" customWidth="1" min="7" max="7"/>
-    <col width="18.85546875" customWidth="1" style="15" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13.28515625" customWidth="1" style="23" min="1" max="1"/>
+    <col width="22.140625" customWidth="1" style="24" min="2" max="2"/>
+    <col width="20.85546875" customWidth="1" style="24" min="3" max="3"/>
+    <col width="36.5703125" customWidth="1" style="24" min="4" max="4"/>
+    <col width="24.5703125" customWidth="1" style="24" min="5" max="6"/>
+    <col width="25.85546875" customWidth="1" style="24" min="7" max="7"/>
+    <col width="18.85546875" customWidth="1" style="8" min="8" max="8"/>
+    <col width="20" customWidth="1" style="24" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="24">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="22" t="inlineStr">
-        <is>
-          <t>ACCOUNT NAME</t>
-        </is>
-      </c>
-      <c r="C1" s="30" t="inlineStr">
-        <is>
-          <t>ACCOUNT NUMBER</t>
-        </is>
-      </c>
-      <c r="D1" s="23" t="inlineStr">
+    <row r="2" customFormat="1" s="10">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>ACCOUNT NAME*</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>ACCOUNT NUMBER*</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E2" s="22" t="inlineStr">
         <is>
           <t>ACCOUNTING CODE</t>
         </is>
       </c>
-      <c r="F1" s="23" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr">
         <is>
           <t>PAYMENT METHOD</t>
         </is>
       </c>
-      <c r="G1" s="30" t="inlineStr">
-        <is>
-          <t>ACCOUNT STATUS</t>
-        </is>
-      </c>
-      <c r="H1" s="26" t="inlineStr">
+      <c r="G2" s="22" t="inlineStr">
+        <is>
+          <t>ACCOUNT STATUS*</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>LIBRARY EDI CODE</t>
         </is>
       </c>
-      <c r="I1" s="23" t="inlineStr">
+      <c r="I2" s="22" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>EBSCO eBooks</t>
-        </is>
-      </c>
-      <c r="C2" s="25" t="n">
-        <v>12345</v>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>eBooks purchased from EBSCO</t>
-        </is>
-      </c>
-      <c r="E2" s="18" t="inlineStr">
-        <is>
-          <t>ACCTSYS-EB</t>
-        </is>
-      </c>
-      <c r="F2" s="18" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GT eBooks</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ACCT-1001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>eBook purchases</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EBK-01</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>EFT</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H2" s="25" t="n">
-        <v>123</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Renew annually in October</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>EBSCO Databases</t>
-        </is>
-      </c>
-      <c r="C3" s="25" t="n">
-        <v>12346</v>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>databases purchased from EBSCO</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>ACCTSYS-DB</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>EFT</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H3" s="25" t="n">
-        <v>456</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>LIB-EDI-01</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Includes EBSCOhost platform access</t>
+          <t>Renews annually in June</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ELSEVIER</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Elsevier Journals</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>55501</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Annual journal subscriptions</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ACCTSYS-EJ</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Credit Card</t>
+          <t>GT Databases</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ACCT-1002</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Active</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>789</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Multi-year agreement</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Northwind Backlist</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>77012</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Backlist title purchases</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ACCTSYS-NW</t>
+          <t>PB Print Books</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ACCT-2001</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1303,88 +1282,56 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>321</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Account closed with contract</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ACMEBIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Binding Services</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>90011</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Ongoing binding and repair services</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ACCTSYS-AB</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Bank Draft</t>
+          <t>PB AV Media</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ACCT-2002</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Active</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>654</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Invoiced monthly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BREPOLS</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brepols Subscriptions</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>44201</v>
+          <t>NSLS Support Plan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ACCT-3001</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Annual journal and series subscriptions</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ACCTSYS-BR</t>
+          <t>Annual support contract</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EFT</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1392,59 +1339,241 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>987</v>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Invoiced annually in January</t>
+          <t>Auto-renews</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BAKERTAYLOR</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B&amp;T Standing Orders</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>60312</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Standing order plan for new releases</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ACCTSYS-BT</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Physical Check</t>
+          <t>NSLS Migration Project</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ACCT-3002</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HPG Binding Services</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ACCT-4001</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bank Draft</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>741</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Reviewed quarterly</t>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HPG Digitization</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ACCT-4002</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Large-format digitization</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Summit Hosting</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ACCT-5001</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Annual hosting subscription</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HOST-01</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>EFT</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Summit Analytics Add-on</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ACCT-5002</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LONESTARPUB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LSP Print Orders</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ACCT-6001</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REDROCKBIND</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RRB Repairs</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ACCT-7001</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AMBERWAVE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AW Periodicals</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ACCT-8001</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WILLOWDATA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>WD Metadata Project</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ACCT-9001</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="G3:G1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"Active,Inactive,Pending"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1455,166 +1584,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A2:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.57" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="10.5703125" customWidth="1" style="24" min="1" max="1"/>
+    <col width="15" customWidth="1" style="24" min="2" max="2"/>
+    <col width="30" customWidth="1" style="24" min="3" max="3"/>
+    <col width="50" customWidth="1" style="24" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="31" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="31" t="inlineStr">
-        <is>
-          <t>NOTE TYPE</t>
-        </is>
-      </c>
-      <c r="C1" s="31" t="inlineStr">
-        <is>
-          <t>NOTE TITLE</t>
-        </is>
-      </c>
-      <c r="D1" s="28" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>NOTE TYPE*</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr">
+        <is>
+          <t>NOTE TITLE*</t>
+        </is>
+      </c>
+      <c r="D2" s="25" t="inlineStr">
         <is>
           <t>CONTENTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Account overview</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Long-standing subscription agent; primary contact is Jan Novak.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EBSCO</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Follow-up</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Renewal timing</t>
+          <t>Account overview</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Renewal negotiations typically start in Q3.</t>
+          <t>Long-standing technology vendor; primary contact is Lan Nguyen.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ELSEVIER</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Follow-up</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Contract terms</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Reviewing multi-year contract terms currently in effect.</t>
+          <t>Renewal timing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Contract discontinued</t>
+          <t>Regional distributor notes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vendor relationship ended 2024; retained for historical records only.</t>
+          <t>Serves the Wichita metro area primarily.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Service scope</t>
+          <t>Support agreement</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Provides cataloging and resource-sharing services across the consortium.</t>
+          <t>Three-year support agreement signed 2024.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BAKERTAYLOR</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Migration test</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Data load verification</t>
+          <t>Service scope</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Added to confirm a brand-new note type is created in FOLIO and notes.json typeId is remapped to its real id on load.</t>
+          <t>Specializes in rare manuscripts and large-format materials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Renewal due soon</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Hosting subscription renews in 60 days; confirm budget approval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FALCONMEDIA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Contract discontinued</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Vendor relationship ended; retained for historical records only.</t>
         </is>
       </c>
     </row>
@@ -1630,43 +1776,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.42578125" customWidth="1" style="8" min="1" max="1"/>
-    <col width="25.42578125" customWidth="1" style="8" min="2" max="2"/>
-    <col width="11.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="16.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="35" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="11.42578125" customWidth="1" style="24" min="1" max="1"/>
+    <col width="25.42578125" customWidth="1" style="24" min="2" max="2"/>
+    <col width="16.140625" bestFit="1" customWidth="1" style="24" min="3" max="3"/>
+    <col width="36" bestFit="1" customWidth="1" style="24" min="4" max="4"/>
+    <col width="35" bestFit="1" customWidth="1" style="24" min="5" max="5"/>
+    <col width="40" bestFit="1" customWidth="1" style="24" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="B1" s="12" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1" s="24">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>NOTE: Unlike the original Organization_Template.xlsx, this sheet holds only the fields that can't repeat. Every address, phone number, email, URL, and alternative name for this organization - including the first one - belongs on the Addresses/Phones/Emails/URLs/Alt names sheet instead.</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1">
-      <c r="B2" s="12" t="n"/>
+    <row r="2" ht="18.75" customHeight="1" s="24">
+      <c r="B2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Coloured columns are mandatory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>ORG NAME</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Columns marked with * are mandatory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" s="24">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>ORG NAME*</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1674,9 +1820,9 @@
           <t>Vendor (Yes/No)</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>ORG status (Active/Inactive/Pending)</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ORG status (Active/Inactive/Pending)*</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1684,21 +1830,21 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
-        <is>
-          <t>ORG TYPE</t>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>ORG TYPE (Choose one or create your own)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>EBSCO Information Services</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>GlobalTech Solutions Inc.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1706,31 +1852,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Subscription agent and database vendor</t>
+          <t>Full-service technology vendor with global reach.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Subscription Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
+          <t>Vendor|Publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" s="24">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ELSEVIER</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Elsevier B.V.</t>
+          <t>Prairie Books &amp; Media</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1745,29 +1891,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Journal and ebook publisher</t>
+          <t>Regional book and media distributor.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>Vendor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FOL-DONOR</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Friends of the Library</t>
+          <t>NorthStar Library Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1777,56 +1923,56 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Local donor organization providing book and material donations</t>
+          <t>Library automation and cataloging services.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Donor</t>
+          <t>Service Provider</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SPRINGHIST</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Springfield Regional History Museum</t>
+          <t>Heritage Preservation Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Museum partner providing archival material loans</t>
+          <t>Archival preservation and conservation services.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Museum</t>
+          <t>Material Supplier</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>SUMMITDATA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Northwind Traders Publishing</t>
+          <t>Summit Data Systems</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1836,34 +1982,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Regional academic publisher, contract discontinued</t>
+          <t>Data hosting and discovery platform provider.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>Access Provider</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ACMEBIND</t>
+          <t>CEDARARCHIVE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Acme Binding &amp; Preservation Services</t>
+          <t>Cedar Archive Foundation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1873,24 +2019,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Book binding, repair, and preservation services</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Service Provider</t>
+          <t>Nonprofit foundation supporting regional archives.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BREPOLS</t>
+          <t>LONESTARPUB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Brepols Publishers</t>
+          <t>Lone Star Publishing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1905,7 +2046,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Belgian academic and humanities publisher</t>
+          <t>Regional publisher of Texas history titles.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1917,44 +2058,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>MOUNTAINVIEW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>Mountain View Consortium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Global library cooperative providing cataloging and resource-sharing services</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Service Provider</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FOLLETT</t>
+          <t>BLUEHORIZON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Follett School Solutions</t>
+          <t>Blue Horizon Media</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1969,29 +2100,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>K-12 library book and materials vendor</t>
+          <t>Streaming and digital media licensing.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Content Provider</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INGRAM</t>
+          <t>GREENFIELD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ingram Library Services</t>
+          <t>Greenfield Historical Society</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2001,24 +2132,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wholesale book distributor and library services provider</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Vendor</t>
+          <t>Local historical society; donor of archival materials.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BAKERTAYLOR</t>
+          <t>REDROCKBIND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Baker &amp; Taylor</t>
+          <t>Red Rock Bindery</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2033,29 +2159,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Book and media distributor for public and academic libraries</t>
+          <t>Book binding and repair services.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Material Supplier</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RIVFRIENDS</t>
+          <t>SILVERLAKE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Friends of Riverside Library</t>
+          <t>Silverlake Digital</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2065,56 +2191,56 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volunteer donor group supporting the Riverside public library</t>
+          <t>Digital repository hosting.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Donor</t>
+          <t>Access Provider</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CITYARCH</t>
+          <t>AMBERWAVE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>City Archives Preservation Society</t>
+          <t>Amberwave Distribution</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nonprofit partner for archival material preservation and loans</t>
+          <t>Wholesale distributor of periodicals.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cultural Institution</t>
+          <t>Vendor</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RILC</t>
+          <t>IRONGATE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Regional Interlibrary Loan Consortium</t>
+          <t>Iron Gate Records Management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2124,29 +2250,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Defunct regional resource-sharing consortium, retained for historical records</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Consortium</t>
+          <t>Off-site records storage.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RIVERSIDE</t>
+          <t>CRYSTALSPR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Riverside Book Exchange</t>
+          <t>Crystal Springs Friends Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2156,24 +2277,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Used and donated book exchange (status column has a typo/invalid value on purpose)</t>
+          <t>Volunteer group supporting the Crystal Springs branch library.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>METRODS</t>
+          <t>TIMBERLINE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Metro Digital Solutions</t>
+          <t>Timberline Learning Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2188,22 +2309,143 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Digital archiving and scanning services vendor</t>
+          <t>K-12 and academic learning resource vendor.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>Content Provider</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>COASTALARCH</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Coastal Archives Cooperative</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Regional cooperative for shared archival storage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WILLOWDATA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Willow Data Services</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Metadata enrichment and data cleanup services.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>Service Provider</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STONEBRIDGE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stonebridge Consortium</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Multi-library resource-sharing consortium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FALCONMEDIA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Falcon Media Group</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Media licensing vendor; contract not renewed.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Content Provider</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="C6:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
     <dataValidation sqref="D6:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Active, Inactive, Pending"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F6:F1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"Access provider,Auction house,Book trade,Consortium,Content provider,Logistics,Material supplier,Membership organization,Private person,Publisher"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2217,134 +2459,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A2:C13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="15.42578125" customWidth="1" min="1" max="1"/>
-    <col width="11.42578125" customWidth="1" style="8" min="2" max="2"/>
-    <col width="13.28515625" customWidth="1" min="3" max="3"/>
+    <col width="15.42578125" customWidth="1" style="24" min="1" max="1"/>
+    <col width="12.7109375" customWidth="1" style="24" min="2" max="2"/>
+    <col width="13.28515625" customWidth="1" style="24" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>ALT NAME</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ALT NAME*</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>EBSCOhost</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EBSCO</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EBSCO Industries</t>
+          <t>GT Solutions</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Common shorthand used internally</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EBSCO</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Elton B. Stephens Company</t>
+          <t>GlobalTech</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Historical legal name</t>
+          <t>Marketing name</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ELSEVIER</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Elsevier Science</t>
+          <t>Prairie Books</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Short form</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Northwind Press</t>
+          <t>PB&amp;M</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NW Press</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Common abbreviation</t>
+          <t>NorthStar</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Online Computer Library Center</t>
+          <t>NSLS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Internal acronym</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FOLLETT</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Follett</t>
+          <t>Heritage Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Acronym</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Summit Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SDS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Acronym</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MOUNTAINVIEW</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MV Consortium</t>
         </is>
       </c>
     </row>
@@ -2359,128 +2657,94 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A2:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20.28515625" customWidth="1" min="1" max="1"/>
-    <col width="13.28515625" customWidth="1" min="6" max="6"/>
-    <col width="10.5703125" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20.28515625" customWidth="1" style="24" min="1" max="1"/>
+    <col width="45.7109375" customWidth="1" style="24" min="2" max="3"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
+    <col width="13.28515625" customWidth="1" style="24" min="6" max="6"/>
+    <col width="14.5703125" customWidth="1" style="24" min="7" max="7"/>
+    <col width="19.42578125" customWidth="1" style="24" min="8" max="8"/>
+    <col width="14" customWidth="1" style="24" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDR1 </t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>ADDR2</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>CITY</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>REGION</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>POSTAL CODE</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>COUNTRY</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-      <c r="I1" s="28" t="inlineStr">
+      <c r="I2" s="25" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10 Estes St</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ipswich</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>01938</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EBSCO</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10 Estes St</t>
+          <t>100 Innovation Way</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Suite 200</t>
+          <t>Suite 400</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01938</t>
+          <t>73301</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2491,70 +2755,80 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>Billing;Shipping</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ELSEVIER</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Radarweg 29</t>
+          <t>PO Box 9821</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TX</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1043 NX</t>
+          <t>73302</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FOL-DONOR</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200 Main St</t>
+          <t>55 Prairie Ave</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Springfield</t>
+          <t>Wichita</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62701</t>
+          <t>67202</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>USA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2566,74 +2840,64 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SPRINGHIST</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>45 Heritage Way</t>
+          <t>600 Warehouse Dr</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Springfield</t>
+          <t>Wichita</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>62702</t>
+          <t>67203</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>USA</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88 Harbor Road</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Floor 4</t>
+          <t>12 Polaris Blvd</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>B3J 1A1</t>
+          <t>55401</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2645,64 +2909,79 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12 Industrial Pkwy</t>
+          <t>12 Polaris Blvd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Floor 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dartmouth</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>B2Y 4M6</t>
+          <t>55401</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Billing</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ACMEBIND</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>500 Industrial Blvd</t>
+          <t>77 Archive Ln</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>02108</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>USA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2714,64 +2993,79 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BREPOLS</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Begijnhof 67</t>
+          <t>77 Archive Ln</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Loading Dock B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Turnhout</t>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>02108</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>SUMMITDATA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6565 Kilgour Place</t>
+          <t>900 Ridge Rd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Building C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43017</t>
+          <t>80202</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>USA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Billing</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2783,101 +3077,96 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FOLLETT</t>
+          <t>SUMMITDATA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1340 Ridgeview Dr</t>
+          <t>900 Ridge Rd</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Building D</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>McHenry</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60050</t>
+          <t>80202</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>USA</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INGRAM</t>
+          <t>CEDARARCHIVE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>One Ingram Blvd</t>
+          <t>4 Cedar Ct</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>La Vergne</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>37086</t>
+          <t>97201</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>USA</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BAKERTAYLOR</t>
+          <t>LONESTARPUB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2810 Coliseum Centre Dr</t>
+          <t>210 Alamo St</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>28217</t>
+          <t>78205</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2894,32 +3183,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RIVFRIENDS</t>
+          <t>BLUEHORIZON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10 Riverside Ave</t>
+          <t>88 Harbor Way</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>92501</t>
+          <t>98101</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>USA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Licensing</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2931,27 +3225,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CITYARCH</t>
+          <t>SILVERLAKE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5 Heritage Sq</t>
+          <t>15 Lakeview Dr</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>WI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>92502</t>
+          <t>53703</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2968,32 +3262,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RILC</t>
+          <t>AMBERWAVE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>400 Consortium Way</t>
+          <t>300 Commerce Pkwy</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>95814</t>
+          <t>43215</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>USA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3005,27 +3304,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RIVERSIDE</t>
+          <t>TIMBERLINE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22 Exchange St</t>
+          <t>42 Ridgeline Rd</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Boise</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>92503</t>
+          <t>83702</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3042,27 +3341,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>METRODS</t>
+          <t>FALCONMEDIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>88 Metro Plaza</t>
+          <t>10 Falcon Ct</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>95815</t>
+          <t>85001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3077,9 +3376,12 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="I3:I1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H3:H1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3092,110 +3394,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A2:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16.7109375" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" style="8" min="2" max="2"/>
-    <col width="10.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16.7109375" customWidth="1" style="24" min="1" max="1"/>
+    <col width="15" customWidth="1" style="24" min="2" max="2"/>
+    <col width="12" bestFit="1" customWidth="1" style="24" min="4" max="4"/>
+    <col width="14" customWidth="1" style="24" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PHONE*</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>978-356-6500</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>978-356-6600</t>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>512-555-0101</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sales;Support</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>512-555-0102</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
           <t>Fax</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>978-356-7000</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Sales;Support</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ELSEVIER</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>+31-20-4853757</t>
+          <t>316-555-0200</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Office</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3207,29 +3499,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SPRINGHIST</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>217-555-0199</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>316-555-0201</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>902-555-0110</t>
+          <t>612-555-0300</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Support</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3241,29 +3548,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>902-555-0120</t>
+          <t>612-555-0301</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ACMEBIND</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>614-555-0134</t>
+          <t>617-555-0400</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Office</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3275,29 +3587,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BREPOLS</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+32-14-448020</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>617-555-0401</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Fax</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>SUMMITDATA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>614-764-6000</t>
+          <t>303-555-0500</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Support</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3309,29 +3631,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FOLLETT</t>
+          <t>SUMMITDATA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>800-621-4272</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>303-555-0501</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INGRAM</t>
+          <t>LONESTARPUB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>615-793-5000</t>
+          <t>210-555-0600</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Office</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3343,12 +3670,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BAKERTAYLOR</t>
+          <t>BLUEHORIZON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>704-998-3100</t>
+          <t>206-555-0700</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Office</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3360,12 +3692,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CITYARCH</t>
+          <t>REDROCKBIND</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>951-555-0110</t>
+          <t>480-555-0800</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Office</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3377,12 +3714,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RIVERSIDE</t>
+          <t>AMBERWAVE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>951-555-0199</t>
+          <t>614-555-0900</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Office</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3394,12 +3736,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>METRODS</t>
+          <t>WILLOWDATA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>916-555-0142</t>
+          <t>651-555-1000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Office</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3411,27 +3758,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>METRODS</t>
+          <t>FALCONMEDIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>916-555-0199</t>
+          <t>602-555-1100</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Landline</t>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="C3:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Office, Mobile, Fax, Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D3:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3444,111 +3799,108 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A2:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18.140625" customWidth="1" min="1" max="1"/>
-    <col width="27.140625" customWidth="1" style="8" min="2" max="2"/>
-    <col width="27.140625" customWidth="1" min="3" max="3"/>
-    <col width="10.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18.140625" customWidth="1" style="24" min="1" max="1"/>
+    <col width="27.140625" customWidth="1" style="24" min="2" max="3"/>
+    <col width="11.140625" bestFit="1" customWidth="1" style="24" min="4" max="4"/>
+    <col width="14" customWidth="1" style="24" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>EMAIL</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EMAIL*</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>LANGUAGE</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="F2" s="25" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>customerservice@ebsco.com</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>vendorsupport@ebsco.com</t>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>info@globaltech.example</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vendor support</t>
+          <t>General inquiries</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Support;Sales</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>sales@ebsco.com</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sales inquiries</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Sales;Marketing</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>billing@globaltech.example</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ELSEVIER</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>journals@elsevier.com</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+          <t>contact@prairiebooks.example</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3557,32 +3909,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FOL-DONOR</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>friends@springfieldlibrary.org</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>orders@prairiebooks.example</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Order desk</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SPRINGHIST</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>archives@springfieldhistory.org</t>
+          <t>help@northstarlib.example</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Support desk</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>eng</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3591,32 +3958,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>orders@northwindtraders.example</t>
+          <t>sales@northstarlib.example</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ACMEBIND</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>service@acmebinding.example</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+          <t>info@heritagepres.example</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3625,32 +3997,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BREPOLS</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>info@brepols.example</t>
+          <t>conservation@heritagepres.example</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Conservation team</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>SUMMITDATA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>support@oclc.example</t>
+          <t>support@summitdata.example</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>24/7 support</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>eng</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3659,32 +4051,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FOLLETT</t>
+          <t>SUMMITDATA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>orders@follett.example</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>accounts@summitdata.example</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INGRAM</t>
+          <t>LONESTARPUB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>libraryservices@ingram.example</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+          <t>orders@lonestarpub.example</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3693,15 +4080,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BAKERTAYLOR</t>
+          <t>BLUEHORIZON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>customercare@bakertaylor.example</t>
+          <t>licensing@bluehorizon.example</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>Licensing</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3710,15 +4102,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RIVFRIENDS</t>
+          <t>REDROCKBIND</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>friends@riversidelibrary.example</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+          <t>service@redrockbind.example</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3727,15 +4119,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CITYARCH</t>
+          <t>SILVERLAKE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>archives@cityarchives.example</t>
+          <t>support@silverlake.example</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3744,15 +4141,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RILC</t>
+          <t>TIMBERLINE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>info@rilc.example</t>
+          <t>sales@timberline.example</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3761,41 +4163,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RIVERSIDE</t>
+          <t>WILLOWDATA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>contact@riversidebooks.example</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>METRODS</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>hello@metrodigital.example</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+          <t>projects@willowdata.example</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D3:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3808,143 +4196,105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A2:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18.140625" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18.140625" customWidth="1" style="24" min="1" max="1"/>
+    <col width="40" customWidth="1" style="24" min="2" max="2"/>
+    <col width="30" customWidth="1" style="24" min="3" max="4"/>
+    <col width="14" customWidth="1" style="24" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="31" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="31" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="C1" s="28" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>URL*</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="D1" s="28" t="inlineStr">
+      <c r="D2" s="25" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-      <c r="F1" s="28" t="inlineStr">
+      <c r="F2" s="25" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://www.ebsco.com</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Corporate homepage</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Requires vendor portal login credentials</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Support;Sales</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EBSCO</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://support.ebsco.com</t>
+          <t>https://www.globaltech.example</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Support portal</t>
+          <t>Corporate site</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Only accessible to registered support accounts</t>
+          <t>Primary marketing site</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Support;Technical</t>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ELSEVIER</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.elsevier.com</t>
+          <t>https://support.globaltech.example</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Publisher homepage</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Support portal</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.northwindtraders.example</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Domain expired; vendor confirmed inactive</t>
+          <t>https://www.prairiebooks.example</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3956,29 +4306,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ACMEBIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.acmebinding.example</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://catalog.prairiebooks.example</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Updated weekly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BREPOLS</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.brepols.example</t>
+          <t>https://www.northstarlib.example</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3990,29 +4345,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.oclc.example</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://status.northstarlib.example</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>System status page</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FOLLETT</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.follett.example</t>
+          <t>https://www.heritagepres.example</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4024,29 +4379,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INGRAM</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.ingramlibrary.example</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://www.heritagepres.example/services</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Services overview</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BAKERTAYLOR</t>
+          <t>SUMMITDATA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.baker-taylor.example</t>
+          <t>https://www.summitdata.example</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4058,24 +4413,61 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>METRODS</t>
+          <t>SUMMITDATA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.metrodigital.example</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+          <t>https://status.summitdata.example</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Uptime status</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BLUEHORIZON</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.bluehorizon.example</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TIMBERLINE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.timberline.example</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="E4:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4088,335 +4480,387 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A2:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.140625" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
-    <col width="11.7109375" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
-    <col width="6.28515625" customWidth="1" min="4" max="4"/>
-    <col width="7.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="23.28515625" customWidth="1" style="8" min="6" max="6"/>
-    <col width="14.42578125" customWidth="1" style="8" min="7" max="7"/>
-    <col width="18.28515625" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" style="24" min="1" max="1"/>
+    <col width="12.140625" bestFit="1" customWidth="1" style="24" min="2" max="2"/>
+    <col width="12.7109375" bestFit="1" customWidth="1" style="24" min="3" max="3"/>
+    <col width="12.42578125" customWidth="1" style="24" min="4" max="4"/>
+    <col width="24.85546875" customWidth="1" style="24" min="5" max="5"/>
+    <col width="23.28515625" customWidth="1" style="24" min="6" max="6"/>
+    <col width="14.42578125" customWidth="1" style="24" min="7" max="7"/>
+    <col width="18.28515625" customWidth="1" style="24" min="8" max="8"/>
+    <col width="13" customWidth="1" style="24" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customFormat="1" customHeight="1" s="3">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>LAST NAME</t>
-        </is>
-      </c>
-      <c r="C1" s="9" t="inlineStr">
-        <is>
-          <t>FIRST NAME</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+    <row r="2" ht="20.25" customFormat="1" customHeight="1" s="3">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>LAST NAME*</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>FIRST NAME*</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">PHONE </t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Novak</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Prefers email over phone</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>jnovak@ebsco.com</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>555-201-0001</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Renewals contact</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Renewals;Support</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20.25" customHeight="1">
+      <c r="J2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="20.25" customHeight="1" s="24">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Rossi</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Mario</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>mrossi@ebsco.com</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>555-201-0002</t>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Lan</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Primary account manager</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>lnguyen@globaltech.example</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>512-555-0111</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Technical support contact</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ELSEVIER</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>de Vries</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Anke</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>a.devries@elsevier.com</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>+31-20-4853700</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Primary account contact</t>
-        </is>
-      </c>
+          <t>Direct line, not general support</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sales;Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20.25" customHeight="1" s="24">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Ortiz</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MacDonald</t>
+          <t>Whitfield</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fiona</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Contract ended 2024, contact for archival questions only</t>
+          <t>Dana</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>fmacdonald@northwindtraders.example</t>
+          <t>dwhitfield@prairiebooks.example</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>902-555-0111</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Rights and permissions contact</t>
+          <t>316-555-0210</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ACMEBIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Reyes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wei</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>wchen@acmebinding.example</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>614-555-0135</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Scheduling and logistics</t>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Handles claims</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Claims</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BREPOLS</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Peeters</t>
+          <t>Park</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Ji-woo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>l.peeters@brepols.example</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>+32-14-448021</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Regional sales contact</t>
+          <t>jpark@northstarlib.example</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RIVERSIDE</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alvarez</t>
+          <t>Adebayo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Femi</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Escalation contact</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>dalvarez@riversidebooks.example</t>
+          <t>fadebayo@northstarlib.example</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>951-555-0198</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Donations contact</t>
+          <t>612-555-0311</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Support</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>METRODS</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Fitzgerald</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tam</t>
+          <t>Maeve</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tnguyen@metrodigital.example</t>
+          <t>mfitzgerald@heritagepres.example</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>916-555-0143</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Primary sales contact</t>
+          <t>617-555-0411</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cohen</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Handles large collections</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alvarez</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Implementation lead</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>salvarez@summitdata.example</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>303-555-0511</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kowalski</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Piotr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LONESTARPUB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Guerra</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>iguerra@lonestarpub.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AMBERWAVE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Novak</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Petra</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>pnovak@amberwave.example</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="H3:H1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4427,131 +4871,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="14.42578125" customWidth="1" style="8" min="2" max="2"/>
-    <col width="11.85546875" customWidth="1" min="3" max="3"/>
-    <col width="35.7109375" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="6"/>
-    <col width="13.28515625" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="13.140625" customWidth="1" min="8" max="8"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" style="24" min="1" max="1"/>
+    <col width="14.42578125" customWidth="1" style="24" min="2" max="2"/>
+    <col width="11.85546875" customWidth="1" style="24" min="3" max="3"/>
+    <col width="35.7109375" customWidth="1" style="24" min="4" max="4"/>
+    <col width="18" customWidth="1" style="24" min="5" max="6"/>
+    <col width="16.140625" customWidth="1" style="24" min="7" max="7"/>
+    <col width="13.140625" customWidth="1" style="24" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="24">
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>If a username is present, a password must be set as well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>DELIVERY METHOD</t>
         </is>
       </c>
-      <c r="F1" s="31" t="inlineStr">
+      <c r="F2" s="25" t="inlineStr">
         <is>
           <t>USERNAME</t>
         </is>
       </c>
-      <c r="G1" s="31" t="inlineStr">
+      <c r="G2" s="25" t="inlineStr">
         <is>
           <t>PASSWORD</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>EBSCO Admin</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>https://eadmin.ebscohost.com/eadmin</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>ebsco_admin_user</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>p@ssw0rd123</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>Administrative interface</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Used by acquisitions staff</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>EBSCONET</t>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>GT Admin Portal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Orders</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ebsconet.com</t>
+          <t>Admin|Orders</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>https://admin.globaltech.example</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4561,71 +4965,59 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>ebsco_order_user</t>
+          <t>gt_admin</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>order_pass456</t>
+          <t>s3cur3-pass</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Ordering and claiming interface</t>
+          <t>Ignored by the schema (no home for it)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Primary interface for order management</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ELSEVIER</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ScienceDirect Admin</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.sciencedirect.com/admin</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>GT Reports Feed</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>https://reports.globaltech.example</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>elsevier_admin</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>sdAdminPass1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Platform administration</t>
-        </is>
-      </c>
+          <t>FTP</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Northwind Ordering Portal</t>
+          <t>PB Order System</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4635,125 +5027,334 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://orders.northwindtraders.example</t>
+          <t>https://orders.prairiebooks.example</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FTP</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>nw_user</t>
+          <t>pb_orders</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nwPass789</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Legacy ordering portal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Decommissioned, kept for reference</t>
+          <t>pb-pass-1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WorldShare Admin</t>
+          <t>PB Invoices</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://worldshare.oclc.example/admin</t>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>oclc_admin</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>wsAdminPass1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Cataloging platform administration</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>METRODS</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Metro Scan Portal</t>
+          <t>NSLS Cataloging Tool</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://cat.northstarlib.example</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ns_admin</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ns-pass-2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Requires VPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NORTHSTARLIB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NSLS Reports</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HPG Order Portal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://portal.metrodigital.example</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://orders.heritagepres.example</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hpg_user</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>hpg-pass-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HPG EDI Feed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Legacy EDI connection, rarely used</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Summit API</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Admin|End user</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://api.summitdata.example</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>summit_api</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>summit-pass-4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>OAuth2 credentials rotate every 90 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Summit Billing Portal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Invoices</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://billing.summitdata.example</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LONESTARPUB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LSP Order Line</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>metro_user</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>metroPass1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Job submission portal</t>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SILVERLAKE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Silverlake Admin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://admin.silverlake.example</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>sl_admin</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>sl-pass-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WILLOWDATA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Willow Project Portal</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>End user</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://portal.willowdata.example</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Online</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Admin, End user, Reports, Orders, Invoices, Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Online, FTP, Email, Other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Organization_Template_Alternate_example_data.xlsx
+++ b/Organization_Template_Alternate_example_data.xlsx
@@ -624,7 +624,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unlike the original Organization_Template.xlsx, Main Org record only holds fields that can't repeat (code, name, vendor flag, status, description). Every address, phone number, email, URL, and alternative name - including the very first one - is entered as its own row on the Addresses/Phones/Emails/URLs/Alt names sheet.</t>
+          <t>Main Org record only holds fields that can't repeat (code, name, vendor flag, status, description). Every address, phone number, email, URL, and alternative name - including the very first one - is entered as its own row on the Addresses/Phones/Emails/URLs/Alt names sheet.</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
     <row r="8">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Please note that coloured columns are mandatory.</t>
+          <t>Please note that columns marked with * are mandatory.</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
     <row r="1" ht="18.75" customHeight="1" s="24">
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>NOTE: Unlike the original Organization_Template.xlsx, this sheet holds only the fields that can't repeat. Every address, phone number, email, URL, and alternative name for this organization - including the first one - belongs on the Addresses/Phones/Emails/URLs/Alt names sheet instead.</t>
+          <t>NOTE: This sheet holds only the fields that can't repeat. Every address, phone number, email, URL, and alternative name for this organization - including the first one - belongs on the Addresses/Phones/Emails/URLs/Alt names sheet instead.</t>
         </is>
       </c>
     </row>
@@ -4179,11 +4179,11 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F3:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D3:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4463,11 +4463,11 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="E4:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F3:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
